--- a/data/trans_orig/IP07C07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C07-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2007 (tasa de respuesta: 88,89%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2007 (tasa de respuesta: 88,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9738</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>22897</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24004</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39248</t>
+          <t>39145</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24704</t>
+          <t>24594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>11362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>26349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42973</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30125</t>
+          <t>29979</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>26327</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>39354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47352</t>
+          <t>48355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65499</t>
+          <t>66564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20485</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>22697</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37812</t>
+          <t>38315</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13060</t>
+          <t>13097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25146</t>
+          <t>24789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27824</t>
+          <t>27863</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48534</t>
+          <t>48543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54161</t>
+          <t>53267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68215</t>
+          <t>68939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44899</t>
+          <t>44910</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59773</t>
+          <t>59590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103733</t>
+          <t>102816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124371</t>
+          <t>123955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,23%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31127</t>
+          <t>31332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>12411</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23329</t>
+          <t>23553</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>18677</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>22612</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38686</t>
+          <t>37438</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20626</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32486</t>
+          <t>32497</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25991</t>
+          <t>26195</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37366</t>
+          <t>37701</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49387</t>
+          <t>49809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66459</t>
+          <t>66809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>793</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18640</t>
+          <t>18541</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>24152</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21751</t>
+          <t>22046</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38409</t>
+          <t>37747</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19377</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21719</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38178</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41179</t>
+          <t>41220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55934</t>
+          <t>56159</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44686</t>
+          <t>44699</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60283</t>
+          <t>59635</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90759</t>
+          <t>90851</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111601</t>
+          <t>111264</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,67%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41491</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62665</t>
+          <t>63703</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>50845</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>73831</t>
+          <t>74238</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>99030</t>
+          <t>99722</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>129499</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>55687</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>77911</t>
+          <t>78536</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>55303</t>
+          <t>55157</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>78170</t>
+          <t>77124</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>116689</t>
+          <t>116514</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>148889</t>
+          <t>149897</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>146177</t>
+          <t>146234</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>174200</t>
+          <t>174610</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>155819</t>
+          <t>155494</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>184475</t>
+          <t>182999</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>311585</t>
+          <t>309451</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>348669</t>
+          <t>348953</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11159</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23393</t>
+          <t>23019</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22829</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39367</t>
+          <t>39628</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14417</t>
+          <t>14400</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30498</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25915</t>
+          <t>26425</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39397</t>
+          <t>39216</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37722</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51872</t>
+          <t>51531</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68553</t>
+          <t>68447</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87572</t>
+          <t>87507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13375</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16729</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>30601</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32458</t>
+          <t>31616</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>38608</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58091</t>
+          <t>57971</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>14762</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27361</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10827</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>22393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46085</t>
+          <t>46317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40177</t>
+          <t>39749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56197</t>
+          <t>55228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40153</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55788</t>
+          <t>56547</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84860</t>
+          <t>85398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>107601</t>
+          <t>108001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,52%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>20680</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33561</t>
+          <t>34588</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15349</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>19995</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34869</t>
+          <t>34424</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37548</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35372</t>
+          <t>35357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48185</t>
+          <t>48100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64869</t>
+          <t>65060</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83601</t>
+          <t>83045</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,86%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>770</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>22018</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36437</t>
+          <t>36835</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39533</t>
+          <t>39706</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>60364</t>
+          <t>59606</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26600</t>
+          <t>26408</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>12272</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25154</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29275</t>
+          <t>28210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47178</t>
+          <t>47481</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>32015</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48685</t>
+          <t>47892</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29715</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45119</t>
+          <t>44881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>66039</t>
+          <t>66795</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>88604</t>
+          <t>88914</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>18063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31168</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>58064</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>82404</t>
+          <t>82407</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>71698</t>
+          <t>70082</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>99194</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>136530</t>
+          <t>135655</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>171172</t>
+          <t>170443</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>58684</t>
+          <t>59393</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>81668</t>
+          <t>82888</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>62822</t>
+          <t>64009</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>107808</t>
+          <t>108704</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>139970</t>
+          <t>140572</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>137310</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>167613</t>
+          <t>166502</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>158383</t>
+          <t>156454</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>185947</t>
+          <t>187922</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>304901</t>
+          <t>303096</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>343086</t>
+          <t>345763</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33543</t>
+          <t>33985</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24766</t>
+          <t>24534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15683</t>
+          <t>15736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28892</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>31340</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49266</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28824</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42583</t>
+          <t>42908</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>22932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36521</t>
+          <t>37422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55521</t>
+          <t>56230</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76743</t>
+          <t>76446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14633</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>20919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31387</t>
+          <t>31958</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>23671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32534</t>
+          <t>32387</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t>50959</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29262</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23596</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39382</t>
+          <t>38303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43949</t>
+          <t>43764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63975</t>
+          <t>64445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35522</t>
+          <t>35074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50799</t>
+          <t>50840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41921</t>
+          <t>41395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58927</t>
+          <t>58240</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82753</t>
+          <t>81668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105077</t>
+          <t>103971</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>511</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19565</t>
+          <t>19667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37717</t>
+          <t>37409</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>23049</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20627</t>
+          <t>20684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23519</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40163</t>
+          <t>40345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28438</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41997</t>
+          <t>42537</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38449</t>
+          <t>38994</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53098</t>
+          <t>53223</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71382</t>
+          <t>71499</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>90495</t>
+          <t>91133</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>946</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32905</t>
+          <t>33416</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31777</t>
+          <t>31203</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>37896</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59764</t>
+          <t>58675</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18095</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33347</t>
+          <t>34518</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>22783</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38258</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>46117</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67269</t>
+          <t>67115</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>36972</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54632</t>
+          <t>53701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33048</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50320</t>
+          <t>50487</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>76342</t>
+          <t>74352</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99795</t>
+          <t>98808</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27397</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>42683</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>62023</t>
+          <t>63153</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>87938</t>
+          <t>88554</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>55151</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>80328</t>
+          <t>81339</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>125396</t>
+          <t>124252</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>162309</t>
+          <t>158861</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>71727</t>
+          <t>70901</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>98993</t>
+          <t>97946</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>83930</t>
+          <t>82862</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>111504</t>
+          <t>111134</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>160324</t>
+          <t>161242</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>202573</t>
+          <t>203389</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>143463</t>
+          <t>142682</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>174969</t>
+          <t>173522</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>151372</t>
+          <t>151390</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>182659</t>
+          <t>182720</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>305095</t>
+          <t>307525</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>351863</t>
+          <t>352295</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
